--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.68249759194722</v>
+        <v>4.010905858691424</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92896564232046</v>
+        <v>3.725956916877075</v>
       </c>
       <c r="E2" t="n">
-        <v>5.090159173505571</v>
+        <v>0.8271508656946552</v>
       </c>
       <c r="F2" t="n">
-        <v>8.972743863399732</v>
+        <v>1.458070877802456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.71599474510786</v>
+        <v>5.316349146080027</v>
       </c>
       <c r="D3" t="n">
-        <v>28.51172809657904</v>
+        <v>4.633155815694094</v>
       </c>
       <c r="E3" t="n">
-        <v>5.090159173505571</v>
+        <v>0.8271508656946552</v>
       </c>
       <c r="F3" t="n">
-        <v>8.972743863399732</v>
+        <v>1.458070877802456</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.44146592987241</v>
+        <v>3.321738213604267</v>
       </c>
       <c r="D4" t="n">
-        <v>7.310562283358322</v>
+        <v>1.187966371045727</v>
       </c>
       <c r="E4" t="n">
-        <v>5.090159173505571</v>
+        <v>0.8271508656946552</v>
       </c>
       <c r="F4" t="n">
-        <v>8.972743863399732</v>
+        <v>1.458070877802456</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
